--- a/tests/fixtures/master_record/synthetic_workbook.xlsx
+++ b/tests/fixtures/master_record/synthetic_workbook.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260331" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260430" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="20260331" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20260430" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,6 +518,11 @@
       <c r="J3" t="n">
         <v>1.0823</v>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026年1月每单位分红 0.05 元, 分红份额 500000 份, 合计收到的现金红利 25000 元</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,6 +549,11 @@
       <c r="J4" t="n">
         <v>1.1542</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026年2月10日, 红利再投资 1234.56 份, 单位净值 1.1542 元. 累计红利再投资份额 10000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -678,6 +688,11 @@
       </c>
       <c r="K9" t="n">
         <v>1000000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>已累计扣除 1500.0 份额作为业绩报酬</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1022,6 +1037,11 @@
       <c r="J4" t="n">
         <v>1.1601</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026年4月10日, 红利再投资 567.89 份, 单位净值 1.1601 元. 累计红利再投资份额 10000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
